--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/IDAHO_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/IDAHO_2013.xlsx
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C113">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C429">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C455">
